--- a/Table_RhoSensitivity.xlsx
+++ b/Table_RhoSensitivity.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,56 +362,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>REML logLik</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>SE (CR2)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tau</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Omega</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Best fit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>213.5786</v>
+        <v>0.1944</v>
       </c>
       <c r="C2">
-        <v>0.1944</v>
+        <v>0.0193</v>
       </c>
       <c r="D2">
-        <v>0.0193</v>
+        <v>0.1536</v>
       </c>
       <c r="E2">
-        <v>0.1536</v>
-      </c>
-      <c r="F2">
         <v>0.1473</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -419,22 +403,16 @@
         <v>0.05</v>
       </c>
       <c r="B3">
-        <v>214.7648</v>
+        <v>0.1922</v>
       </c>
       <c r="C3">
-        <v>0.1922</v>
+        <v>0.0191</v>
       </c>
       <c r="D3">
-        <v>0.0191</v>
+        <v>0.1504</v>
       </c>
       <c r="E3">
-        <v>0.1504</v>
-      </c>
-      <c r="F3">
         <v>0.1481</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -442,22 +420,16 @@
         <v>0.1</v>
       </c>
       <c r="B4">
-        <v>215.8439</v>
+        <v>0.1902</v>
       </c>
       <c r="C4">
-        <v>0.1902</v>
+        <v>0.019</v>
       </c>
       <c r="D4">
-        <v>0.019</v>
+        <v>0.1473</v>
       </c>
       <c r="E4">
-        <v>0.1473</v>
-      </c>
-      <c r="F4">
         <v>0.1489</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -465,22 +437,16 @@
         <v>0.15</v>
       </c>
       <c r="B5">
-        <v>216.8189</v>
+        <v>0.1881</v>
       </c>
       <c r="C5">
-        <v>0.1881</v>
+        <v>0.0189</v>
       </c>
       <c r="D5">
-        <v>0.0189</v>
+        <v>0.1443</v>
       </c>
       <c r="E5">
-        <v>0.1443</v>
-      </c>
-      <c r="F5">
         <v>0.1498</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -488,22 +454,16 @@
         <v>0.2</v>
       </c>
       <c r="B6">
-        <v>217.6895</v>
+        <v>0.1861</v>
       </c>
       <c r="C6">
-        <v>0.1861</v>
+        <v>0.0188</v>
       </c>
       <c r="D6">
-        <v>0.0188</v>
+        <v>0.1414</v>
       </c>
       <c r="E6">
-        <v>0.1414</v>
-      </c>
-      <c r="F6">
         <v>0.1507</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -511,22 +471,16 @@
         <v>0.25</v>
       </c>
       <c r="B7">
-        <v>218.4527</v>
+        <v>0.1842</v>
       </c>
       <c r="C7">
-        <v>0.1842</v>
+        <v>0.0187</v>
       </c>
       <c r="D7">
-        <v>0.0187</v>
+        <v>0.1387</v>
       </c>
       <c r="E7">
-        <v>0.1387</v>
-      </c>
-      <c r="F7">
         <v>0.1517</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -534,22 +488,16 @@
         <v>0.3</v>
       </c>
       <c r="B8">
-        <v>219.1041</v>
+        <v>0.1823</v>
       </c>
       <c r="C8">
-        <v>0.1823</v>
+        <v>0.0186</v>
       </c>
       <c r="D8">
-        <v>0.0186</v>
+        <v>0.136</v>
       </c>
       <c r="E8">
-        <v>0.136</v>
-      </c>
-      <c r="F8">
         <v>0.1527</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -557,22 +505,16 @@
         <v>0.35</v>
       </c>
       <c r="B9">
-        <v>219.6371</v>
+        <v>0.1804</v>
       </c>
       <c r="C9">
-        <v>0.1804</v>
+        <v>0.0185</v>
       </c>
       <c r="D9">
-        <v>0.0185</v>
+        <v>0.1335</v>
       </c>
       <c r="E9">
-        <v>0.1335</v>
-      </c>
-      <c r="F9">
         <v>0.1537</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -580,22 +522,16 @@
         <v>0.4</v>
       </c>
       <c r="B10">
-        <v>220.0442</v>
+        <v>0.1786</v>
       </c>
       <c r="C10">
-        <v>0.1786</v>
+        <v>0.0184</v>
       </c>
       <c r="D10">
-        <v>0.0184</v>
+        <v>0.1311</v>
       </c>
       <c r="E10">
-        <v>0.1311</v>
-      </c>
-      <c r="F10">
         <v>0.1549</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -603,22 +539,16 @@
         <v>0.45</v>
       </c>
       <c r="B11">
-        <v>220.3161</v>
+        <v>0.1768</v>
       </c>
       <c r="C11">
-        <v>0.1768</v>
+        <v>0.0183</v>
       </c>
       <c r="D11">
-        <v>0.0183</v>
+        <v>0.1287</v>
       </c>
       <c r="E11">
-        <v>0.1287</v>
-      </c>
-      <c r="F11">
         <v>0.156</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -626,22 +556,16 @@
         <v>0.5</v>
       </c>
       <c r="B12">
-        <v>220.4422</v>
+        <v>0.1751</v>
       </c>
       <c r="C12">
-        <v>0.1751</v>
+        <v>0.0183</v>
       </c>
       <c r="D12">
-        <v>0.0183</v>
+        <v>0.1265</v>
       </c>
       <c r="E12">
-        <v>0.1265</v>
-      </c>
-      <c r="F12">
         <v>0.1573</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -649,22 +573,16 @@
         <v>0.55</v>
       </c>
       <c r="B13">
-        <v>220.4105</v>
+        <v>0.1734</v>
       </c>
       <c r="C13">
-        <v>0.1734</v>
+        <v>0.0182</v>
       </c>
       <c r="D13">
-        <v>0.0182</v>
+        <v>0.1244</v>
       </c>
       <c r="E13">
-        <v>0.1244</v>
-      </c>
-      <c r="F13">
         <v>0.1587</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -672,22 +590,16 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="B14">
-        <v>220.2074</v>
+        <v>0.1718</v>
       </c>
       <c r="C14">
-        <v>0.1718</v>
+        <v>0.0182</v>
       </c>
       <c r="D14">
-        <v>0.0182</v>
+        <v>0.1223</v>
       </c>
       <c r="E14">
-        <v>0.1223</v>
-      </c>
-      <c r="F14">
         <v>0.1601</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -695,22 +607,16 @@
         <v>0.65</v>
       </c>
       <c r="B15">
-        <v>219.8181</v>
+        <v>0.1702</v>
       </c>
       <c r="C15">
-        <v>0.1702</v>
+        <v>0.0181</v>
       </c>
       <c r="D15">
-        <v>0.0181</v>
+        <v>0.1203</v>
       </c>
       <c r="E15">
-        <v>0.1203</v>
-      </c>
-      <c r="F15">
         <v>0.1616</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -718,22 +624,16 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B16">
-        <v>219.2258</v>
+        <v>0.1686</v>
       </c>
       <c r="C16">
-        <v>0.1686</v>
+        <v>0.0181</v>
       </c>
       <c r="D16">
-        <v>0.0181</v>
+        <v>0.1184</v>
       </c>
       <c r="E16">
-        <v>0.1184</v>
-      </c>
-      <c r="F16">
         <v>0.1633</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -741,22 +641,16 @@
         <v>0.75</v>
       </c>
       <c r="B17">
-        <v>218.412</v>
+        <v>0.1671</v>
       </c>
       <c r="C17">
-        <v>0.1671</v>
+        <v>0.0181</v>
       </c>
       <c r="D17">
-        <v>0.0181</v>
+        <v>0.1165</v>
       </c>
       <c r="E17">
-        <v>0.1165</v>
-      </c>
-      <c r="F17">
         <v>0.1651</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -764,22 +658,16 @@
         <v>0.8</v>
       </c>
       <c r="B18">
-        <v>217.3566</v>
+        <v>0.1656</v>
       </c>
       <c r="C18">
-        <v>0.1656</v>
+        <v>0.018</v>
       </c>
       <c r="D18">
-        <v>0.018</v>
+        <v>0.1147</v>
       </c>
       <c r="E18">
-        <v>0.1147</v>
-      </c>
-      <c r="F18">
         <v>0.167</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -787,22 +675,16 @@
         <v>0.8500000000000001</v>
       </c>
       <c r="B19">
-        <v>216.0373</v>
+        <v>0.1641</v>
       </c>
       <c r="C19">
-        <v>0.1641</v>
+        <v>0.018</v>
       </c>
       <c r="D19">
-        <v>0.018</v>
+        <v>0.1128</v>
       </c>
       <c r="E19">
-        <v>0.1128</v>
-      </c>
-      <c r="F19">
         <v>0.1691</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -810,22 +692,16 @@
         <v>0.9</v>
       </c>
       <c r="B20">
-        <v>214.4298</v>
+        <v>0.1626</v>
       </c>
       <c r="C20">
-        <v>0.1626</v>
+        <v>0.018</v>
       </c>
       <c r="D20">
-        <v>0.018</v>
+        <v>0.111</v>
       </c>
       <c r="E20">
-        <v>0.111</v>
-      </c>
-      <c r="F20">
         <v>0.1713</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -833,22 +709,16 @@
         <v>0.95</v>
       </c>
       <c r="B21">
-        <v>212.5075</v>
+        <v>0.1612</v>
       </c>
       <c r="C21">
-        <v>0.1612</v>
+        <v>0.018</v>
       </c>
       <c r="D21">
-        <v>0.018</v>
+        <v>0.1091</v>
       </c>
       <c r="E21">
-        <v>0.1091</v>
-      </c>
-      <c r="F21">
         <v>0.1738</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
